--- a/frontend/test_students.xlsx
+++ b/frontend/test_students.xlsx
@@ -397,20 +397,38 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:J4"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
         <v>Student Name</v>
       </c>
       <c r="B1" t="str">
+        <v>Roll Number</v>
+      </c>
+      <c r="C1" t="str">
         <v>Class &amp; Section</v>
       </c>
-      <c r="C1" t="str">
+      <c r="D1" t="str">
+        <v>Phone Number</v>
+      </c>
+      <c r="E1" t="str">
+        <v>Parent Name</v>
+      </c>
+      <c r="F1" t="str">
+        <v>District</v>
+      </c>
+      <c r="G1" t="str">
+        <v>State</v>
+      </c>
+      <c r="H1" t="str">
+        <v>City</v>
+      </c>
+      <c r="I1" t="str">
+        <v>Pincode</v>
+      </c>
+      <c r="J1" t="str">
         <v>Risk Level</v>
-      </c>
-      <c r="D1" t="str">
-        <v>Reason / Note</v>
       </c>
     </row>
     <row r="2">
@@ -418,13 +436,31 @@
         <v>Ramesh Kumar</v>
       </c>
       <c r="B2" t="str">
+        <v>HM10105</v>
+      </c>
+      <c r="C2" t="str">
         <v>Class 10A</v>
       </c>
-      <c r="C2" t="str">
+      <c r="D2" t="str">
+        <v>9876543210</v>
+      </c>
+      <c r="E2" t="str">
+        <v>Kumarasamy K.</v>
+      </c>
+      <c r="F2" t="str">
+        <v>Coimbatore</v>
+      </c>
+      <c r="G2" t="str">
+        <v>Tamil Nadu</v>
+      </c>
+      <c r="H2" t="str">
+        <v>Coimbatore</v>
+      </c>
+      <c r="I2" t="str">
+        <v>641001</v>
+      </c>
+      <c r="J2" t="str">
         <v>High</v>
-      </c>
-      <c r="D2" t="str">
-        <v>Failed to attend EMIS profile update</v>
       </c>
     </row>
     <row r="3">
@@ -432,13 +468,31 @@
         <v>Anitha S.</v>
       </c>
       <c r="B3" t="str">
+        <v>HM11202</v>
+      </c>
+      <c r="C3" t="str">
         <v>Class 11B</v>
       </c>
-      <c r="C3" t="str">
+      <c r="D3" t="str">
+        <v>9876543212</v>
+      </c>
+      <c r="E3" t="str">
+        <v>Senthil S.</v>
+      </c>
+      <c r="F3" t="str">
+        <v>Coimbatore</v>
+      </c>
+      <c r="G3" t="str">
+        <v>Tamil Nadu</v>
+      </c>
+      <c r="H3" t="str">
+        <v>Coimbatore</v>
+      </c>
+      <c r="I3" t="str">
+        <v>641003</v>
+      </c>
+      <c r="J3" t="str">
         <v>Medium</v>
-      </c>
-      <c r="D3" t="str">
-        <v>Repeated absent warnings from teacher</v>
       </c>
     </row>
     <row r="4">
@@ -446,18 +500,36 @@
         <v/>
       </c>
       <c r="B4" t="str">
+        <v>HM12101</v>
+      </c>
+      <c r="C4" t="str">
         <v>Class 12A</v>
       </c>
-      <c r="C4" t="str">
-        <v>Low</v>
-      </c>
       <c r="D4" t="str">
-        <v>Missing name test</v>
+        <v>9876543215</v>
+      </c>
+      <c r="E4" t="str">
+        <v>Ramasamy A.</v>
+      </c>
+      <c r="F4" t="str">
+        <v>Coimbatore</v>
+      </c>
+      <c r="G4" t="str">
+        <v>Tamil Nadu</v>
+      </c>
+      <c r="H4" t="str">
+        <v>Coimbatore</v>
+      </c>
+      <c r="I4" t="str">
+        <v>641004</v>
+      </c>
+      <c r="J4" t="str">
+        <v>Medium</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D4"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:J4"/>
   </ignoredErrors>
 </worksheet>
 </file>